--- a/통합 문서1.xlsx
+++ b/통합 문서1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\it\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C928EEB1-32F5-40E3-91D0-F076A7B427D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBCB8AA4-F928-4354-A8B7-5C854EC1FCDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{BDE8B957-CFD8-48A6-A835-61441740D43D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{BDE8B957-CFD8-48A6-A835-61441740D43D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -955,30 +955,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94CC9280-92FB-422C-AB14-BEA89069714F}">
   <dimension ref="A1:W44"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.75" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.75" customWidth="1"/>
     <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.125" customWidth="1"/>
-    <col min="9" max="9" width="15.625" customWidth="1"/>
-    <col min="10" max="10" width="17.375" customWidth="1"/>
-    <col min="15" max="15" width="17.875" customWidth="1"/>
-    <col min="16" max="16" width="5.125" customWidth="1"/>
-    <col min="17" max="17" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.08203125" customWidth="1"/>
+    <col min="9" max="9" width="15.58203125" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" customWidth="1"/>
+    <col min="15" max="15" width="17.83203125" customWidth="1"/>
+    <col min="16" max="16" width="5.08203125" customWidth="1"/>
+    <col min="17" max="17" width="18.83203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="16" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.08203125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="3.75" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="8.75" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="11.25" customWidth="1"/>
     <col min="23" max="23" width="23.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>156</v>
       </c>
@@ -998,7 +998,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1125,7 +1125,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>23</v>
       </c>
@@ -1438,7 +1438,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -1568,7 +1568,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1633,7 +1633,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -1916,7 +1916,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -1960,7 +1960,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>53</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>55</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>110</v>
       </c>
@@ -2224,7 +2224,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>62</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>112</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -2356,7 +2356,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>68</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>70</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>72</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>74</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>76</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>80</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>83</v>
       </c>
@@ -2561,7 +2561,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>85</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>87</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>89</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>91</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>94</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>97</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>100</v>
       </c>
@@ -2722,7 +2722,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>103</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>106</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>108</v>
       </c>
